--- a/data/trans_dic/P1435_2011_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1435_2011_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,59</t>
+          <t>0,78; 2,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,74</t>
+          <t>1,92; 4,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,03</t>
+          <t>6,54; 9,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,54</t>
+          <t>1,07; 2,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,04</t>
+          <t>4,07; 5,93</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,14</t>
+          <t>0,95; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,68</t>
+          <t>3,08; 5,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,31</t>
+          <t>7,44; 10,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,89</t>
+          <t>1,54; 2,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,69</t>
+          <t>4,5; 6,14</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,17</t>
+          <t>0,14; 1,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,98</t>
+          <t>0,37; 1,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,0</t>
+          <t>2,3; 5,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 61,98</t>
+          <t>7,15; 10,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,91</t>
+          <t>1,37; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 45,19</t>
+          <t>3,98; 6,03</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,02</t>
+          <t>0,1; 1,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,37</t>
+          <t>1,57; 3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,57</t>
+          <t>2,24; 4,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 11,65</t>
+          <t>8,36; 11,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,6</t>
+          <t>1,36; 2,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 7,64</t>
+          <t>5,45; 7,37</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -957,27 +957,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,26; 2,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,23</t>
+          <t>3,01; 4,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 28,64</t>
+          <t>8,25; 9,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,32</t>
+          <t>1,64; 2,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 18,81</t>
+          <t>4,94; 5,93</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64704</t>
+          <t>69285</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6370</t>
+          <t>0; 8337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5096; 16454</t>
+          <t>5418; 17260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12883; 33055</t>
+          <t>13401; 33189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45823; 67735</t>
+          <t>47946; 72053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15302; 35514</t>
+          <t>14961; 35405</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53466; 79204</t>
+          <t>57870; 84380</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84405</t>
+          <t>94502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>111732</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4763</t>
+          <t>0; 4297</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6370; 25474</t>
+          <t>9928; 27132</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31167; 58660</t>
+          <t>31793; 58727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70992; 98668</t>
+          <t>79615; 110527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31989; 59289</t>
+          <t>31580; 58864</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64393; 122325</t>
+          <t>95259; 130190</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262464</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>268939</t>
+          <t>78965</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1053; 8891</t>
+          <t>1045; 10054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2922; 13894</t>
+          <t>2929; 14642</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18249; 38876</t>
+          <t>17856; 40307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67937; 577648</t>
+          <t>57958; 88921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22203; 44662</t>
+          <t>21063; 44608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68420; 738883</t>
+          <t>64185; 97215</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105237</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>129997</t>
+          <t>133331</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>973; 9679</t>
+          <t>981; 9445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15393; 40444</t>
+          <t>15555; 38736</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24228; 48096</t>
+          <t>23550; 48187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81784; 127126</t>
+          <t>93358; 125915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26445; 51952</t>
+          <t>27118; 50568</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107031; 154119</t>
+          <t>114744; 155080</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5833; 19341</t>
+          <t>5913; 19055</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39830; 75382</t>
+          <t>44605; 76856</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105213; 150344</t>
+          <t>106935; 151587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310448; 1046860</t>
+          <t>307501; 364220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>114320; 161872</t>
+          <t>114317; 162651</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>358827; 1338126</t>
+          <t>358755; 430079</t>
         </is>
       </c>
     </row>
